--- a/app/src/main/java/com/example/methodmesh/modules/odkformlauncher/docs/example_odk_odk_form_launcher.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/odkformlauncher/docs/example_odk_odk_form_launcher.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Re0a8f1dc0b7b426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" r:id="R31ba63f831734545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra74a94d257cc4dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" r:id="R9aff38b601d44aa0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,19 +14,30 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -35,8 +46,11 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1000,38 +1014,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">form_title</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="A1" s="3" t="str">
+        <x:v>form_title</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>version</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
         <x:v>MethodMesh Multimethod Protocol Workflow</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">form_id</x:t>
-        </x:is>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>methodmesh_protocol_multimethod_workflow</x:v>
       </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2026090702</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">version</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A3"/>
+      <x:c r="B3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
